--- a/files/港岛-北角-柏蔚山.xlsx
+++ b/files/港岛-北角-柏蔚山.xlsx
@@ -28984,10 +28984,47 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>33/F</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr"/>
+      <c r="C7" s="16" t="inlineStr"/>
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="16" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>F | 899呎 (3房)
+$2,809万
+$31,244/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>G | 615呎 (2房)
+$2,371万
+$38,551/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>H | 617呎 (2房)
+$2,265万
+$36,707/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>33&amp;35/F</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>A | 3136呎 (4+房)
 $17,716万
@@ -28995,7 +29032,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>B | 2334呎 (4+房)
 $8,578万
@@ -29003,7 +29040,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>C | 2375呎 (4+房)
 $11,875万
@@ -29011,48 +29048,11 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
-      <c r="J7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
       <c r="E8" s="16" t="inlineStr"/>
       <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 899呎 (3房)
-$2,809万
-$31,244/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 615呎 (2房)
-$2,371万
-$38,551/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 617呎 (2房)
-$2,265万
-$36,707/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="G8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr"/>
+      <c r="I8" s="16" t="inlineStr"/>
       <c r="J8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
@@ -31039,10 +31039,46 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>33/F</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>B | 1014呎 (4+房)
+$4,398万
+$43,370/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="16" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>F | 1048呎 (4+房)
+$4,284万
+$40,874/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>G | 1075呎 (4+房)
+$3,477万
+$32,347/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>33&amp;35/F</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>A | 2058呎 (4+房)
 $10,496万
@@ -31050,8 +31086,8 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>C | 1856呎 (4+房)
 $9,317万
@@ -31059,8 +31095,8 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>E | 2028呎 (4+房)
 $10,500万
@@ -31068,44 +31104,8 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1014呎 (4+房)
-$4,398万
-$43,370/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 1048呎 (4+房)
-$4,284万
-$40,874/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 1075呎 (4+房)
-$3,477万
-$32,347/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="G8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr"/>
       <c r="I8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
@@ -32914,10 +32914,54 @@
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>33/F</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr"/>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>B | 662呎 (1房)
+$2,895万
+$43,731/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr"/>
+      <c r="E7" s="16" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>F | 908呎 (3房)
+$2,902万
+$31,961/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>G | 908呎 (3房)
+$2,840万
+$31,278/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>H | 834呎 (3房)
+$2,659万
+$31,880/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>33&amp;35/F</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>A | 2503呎 (4+房)
 $12,510万
@@ -32925,8 +32969,8 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>C | 1624呎 (4+房)
 $8,206万
@@ -32934,7 +32978,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>D | 2282呎 (4+房)
 $11,684万
@@ -32942,54 +32986,10 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
-      <c r="J7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 662呎 (1房)
-$2,895万
-$43,731/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr"/>
       <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 908呎 (3房)
-$2,902万
-$31,961/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 908呎 (3房)
-$2,840万
-$31,278/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 834呎 (3房)
-$2,659万
-$31,880/呎
-(已售)</t>
-        </is>
-      </c>
+      <c r="G8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr"/>
+      <c r="I8" s="16" t="inlineStr"/>
       <c r="J8" s="16" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">

--- a/files/港岛-北角-柏蔚山.xlsx
+++ b/files/港岛-北角-柏蔚山.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,14 +46,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -65,7 +70,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -76,7 +81,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -87,7 +92,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -97,9 +102,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -147,8 +173,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -195,19 +221,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,13 +239,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -609,7 +647,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -28806,2048 +28844,2048 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>柏蔚山 - 1座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>211 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>211 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
-$2,865万
+$2865万
 $31,869/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
-$2,513万
+$2513万
 $40,863/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$2,401万
+$2401万
 $38,909/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 3136呎 (4+房)
+$17716万
+$56,491/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2334呎 (4+房)
+$8578万
+$36,752/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 2375呎 (4+房)
+$11875万
+$50,000/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
-$2,809万
+$2809万
 $31,244/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
-$2,371万
+$2371万
 $38,551/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$2,265万
+$2265万
 $36,707/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>33&amp;35/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 3136呎 (4+房)
-$17,716万
-$56,491/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 2334呎 (4+房)
-$8,578万
-$36,752/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 2375呎 (4+房)
-$11,875万
-$50,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr"/>
-      <c r="H8" s="16" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
-      <c r="J8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 1485呎 (4+房)
-$6,687万
+$6687万
 $45,028/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 1201呎 (4+房)
-$5,058万
+$5058万
 $42,116/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 1362呎 (4+房)
-$5,609万
+$5609万
 $41,184/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
-$2,757万
+$2757万
 $30,665/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
-$2,280万
+$2280万
 $37,068/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$2,232万
+$2232万
 $36,177/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>J | 803呎 (3房)
-$2,438万
+$2438万
 $30,361/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 1485呎 (4+房)
-$6,273万
+$6273万
 $42,242/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 1201呎 (4+房)
-$4,817万
+$4817万
 $40,111/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 1362呎 (4+房)
-$5,342万
+$5342万
 $39,222/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
-$2,703万
+$2703万
 $30,065/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
-$2,159万
+$2159万
 $35,111/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$2,114万
+$2114万
 $34,266/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>J | 803呎 (3房)
-$2,390万
+$2390万
 $29,766/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1485呎 (4+房)
-$5,870万
+$5870万
 $39,530/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 1202呎 (4+房)
-$4,508万
+$4508万
 $37,503/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 1362呎 (4+房)
-$4,999万
+$4999万
 $36,703/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr"/>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
-$2,650万
+$2650万
 $29,474/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 614呎 (2房)
-$2,117万
+$2117万
 $34,479/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$2,073万
+$2073万
 $33,595/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>J | 803呎 (3房)
-$2,343万
+$2343万
 $29,183/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 1485呎 (4+房)
-$5,104万
+$5104万
 $34,374/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 1201呎 (4+房)
-$3,954万
+$3954万
 $32,925/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 1362呎 (4+房)
-$4,901万
+$4901万
 $35,984/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
-$2,598万
+$2598万
 $28,897/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 614呎 (2房)
-$2,076万
+$2076万
 $33,803/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$2,032万
+$2032万
 $32,935/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>J | 803呎 (3房)
-$2,297万
+$2297万
 $28,610/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 1487呎 (4+房)
-$5,104万
+$5104万
 $34,328/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 1201呎 (4+房)
-$3,954万
+$3954万
 $32,925/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 1362呎 (4+房)
-$3,710万
+$3710万
 $27,239/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
-$2,598万
+$2598万
 $28,897/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
-$2,076万
+$2076万
 $33,748/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$2,032万
+$2032万
 $32,935/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>J | 803呎 (3房)
-$2,297万
+$2297万
 $28,610/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 1487呎 (4+房)
-$5,077万
+$5077万
 $34,140/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 1201呎 (4+房)
-$3,933万
+$3933万
 $32,745/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 1362呎 (4+房)
-$4,985万
+$4985万
 $36,601/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
-$2,508万
+$2508万
 $27,893/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
-$2,003万
+$2003万
 $32,574/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,962万
+$1962万
 $31,793/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>J | 803呎 (3房)
-$2,335万
+$2335万
 $29,083/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 1485呎 (4+房)
-$4,812万
+$4812万
 $32,404/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 1202呎 (4+房)
-$3,728万
+$3728万
 $31,012/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 1362呎 (4+房)
-$5,408万
+$5408万
 $39,709/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 899呎 (3房)
-$2,458万
+$2458万
 $27,346/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 615呎 (2房)
-$1,964万
+$1964万
 $31,935/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$2,284万
+$2284万
 $37,013/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>J | 803呎 (3房)
-$2,174万
+$2174万
 $27,075/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,363万
+$2363万
 $28,434/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,250万
+$2250万
 $28,159/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,612万
+$2612万
 $33,438/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 783呎 (3房)
-$2,205万
+$2205万
 $28,158/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,431万
+$2431万
 $28,435/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,429万
+$2429万
 $26,809/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,916万
+$1916万
 $31,057/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,867万
+$1867万
 $30,261/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,145万
+$2145万
 $26,545/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,294万
+$2294万
 $27,605/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,184万
+$2184万
 $27,339/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,135万
+$2135万
 $27,338/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$2,141万
+$2141万
 $27,408/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,360万
+$2360万
 $27,607/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,393万
+$2393万
 $26,413/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,888万
+$1888万
 $30,598/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,840万
+$1840万
 $29,814/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,113万
+$2113万
 $26,152/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,227万
+$2227万
 $26,801/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,121万
+$2121万
 $26,542/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,073万
+$2073万
 $26,542/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 783呎 (3房)
-$2,078万
+$2078万
 $26,543/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,292万
+$2292万
 $26,802/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,358万
+$2358万
 $26,022/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,860万
+$1860万
 $30,146/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,812万
+$1812万
 $29,373/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,082万
+$2082万
 $25,765/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,322万
+$2322万
 $27,947/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,100万
+$2100万
 $26,279/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,052万
+$2052万
 $26,279/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$2,058万
+$2058万
 $26,346/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,269万
+$2269万
 $26,537/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,323万
+$2323万
 $25,638/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,832万
+$1832万
 $29,700/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,786万
+$1786万
 $28,938/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,051万
+$2051万
 $25,385/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,183万
+$2183万
 $26,274/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,079万
+$2079万
 $26,019/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,032万
+$2032万
 $26,019/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$2,037万
+$2037万
 $26,086/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,246万
+$2246万
 $26,274/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,288万
+$2288万
 $25,259/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,805万
+$1805万
 $29,261/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,759万
+$1759万
 $28,511/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J20" s="17" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,021万
+$2021万
 $25,010/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,162万
+$2162万
 $26,014/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,058万
+$2058万
 $25,762/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,012万
+$2012万
 $25,762/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$2,017万
+$2017万
 $25,828/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,224万
+$2224万
 $26,014/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,704万
+$2704万
 $29,845/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,796万
+$1796万
 $29,115/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,750万
+$1750万
 $28,370/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J21" s="17" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,474万
+$2474万
 $30,616/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,277万
+$2277万
 $27,396/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,058万
+$2058万
 $25,762/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,012万
+$2012万
 $25,762/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$2,017万
+$2017万
 $25,828/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,224万
+$2224万
 $26,014/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,704万
+$2704万
 $29,845/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,796万
+$1796万
 $29,115/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,750万
+$1750万
 $28,370/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J22" s="17" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,462万
+$2462万
 $30,465/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,119万
+$2119万
 $25,504/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,018万
+$2018万
 $25,257/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$1,972万
+$1972万
 $25,256/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$1,978万
+$1978万
 $25,321/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,181万
+$2181万
 $25,504/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,348万
+$2348万
 $25,912/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,779万
+$1779万
 $28,828/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,733万
+$1733万
 $28,088/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,063万
+$2063万
 $25,527/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,098万
+$2098万
 $25,252/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$1,998万
+$1998万
 $25,006/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$1,953万
+$1953万
 $25,006/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$2,325万
+$2325万
 $29,771/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,564万
+$2564万
 $29,986/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,774万
+$2774万
 $30,617/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,770万
+$1770万
 $28,684/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,724万
+$1724万
 $27,948/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J24" s="17" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,052万
+$2052万
 $25,400/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,163万
+$2163万
 $26,032/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,060万
+$2060万
 $25,780/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,013万
+$2013万
 $25,780/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$2,018万
+$2018万
 $25,845/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,226万
+$2226万
 $26,033/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,760万
+$2760万
 $30,464/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,761万
+$1761万
 $28,541/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,716万
+$1716万
 $27,809/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J25" s="17" t="inlineStr">
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,151万
+$2151万
 $26,616/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,152万
+$2152万
 $25,903/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,050万
+$2050万
 $25,652/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,003万
+$2003万
 $25,652/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 783呎 (3房)
-$2,008万
+$2008万
 $25,651/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,215万
+$2215万
 $25,903/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,313万
+$2313万
 $25,526/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,752万
+$1752万
 $28,399/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,707万
+$1707万
 $27,671/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J26" s="17" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,032万
+$2032万
 $25,149/呎
 (18年-06月)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,142万
+$2142万
 $25,774/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,039万
+$2039万
 $25,523/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$1,993万
+$1993万
 $25,524/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$1,998万
+$1998万
 $25,589/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,204万
+$2204万
 $25,773/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,301万
+$2301万
 $25,400/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,744万
+$1744万
 $28,258/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,699万
+$1699万
 $27,533/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,022万
+$2022万
 $25,022/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,131万
+$2131万
 $25,646/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,029万
+$2029万
 $25,397/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$1,984万
+$1984万
 $25,397/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$2,362万
+$2362万
 $30,237/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,193万
+$2193万
 $25,646/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,290万
+$2290万
 $25,273/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,735万
+$1735万
 $28,117/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,690万
+$1690万
 $27,397/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J28" s="17" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,012万
+$2012万
 $24,899/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,120万
+$2120万
 $25,517/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,019万
+$2019万
 $25,270/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$2,344万
+$2344万
 $30,009/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$1,979万
+$1979万
 $25,335/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,182万
+$2182万
 $25,518/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,284万
+$2284万
 $25,210/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,730万
+$1730万
 $28,047/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,686万
+$1686万
 $27,327/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J29" s="17" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,007万
+$2007万
 $24,837/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,518万
+$2518万
 $30,302/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$2,019万
+$2019万
 $25,270/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$1,964万
+$1964万
 $25,145/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$1,969万
+$1969万
 $25,209/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,182万
+$2182万
 $25,518/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,284万
+$2284万
 $25,210/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,730万
+$1730万
 $28,047/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,686万
+$1686万
 $27,327/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J30" s="17" t="inlineStr">
+      <c r="J29" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$2,007万
+$2007万
 $24,837/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,100万
+$2100万
 $25,266/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$1,999万
+$1999万
 $25,021/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$1,954万
+$1954万
 $25,019/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 781呎 (3房)
-$1,959万
+$1959万
 $25,085/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,160万
+$2160万
 $25,265/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,273万
+$2273万
 $25,085/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H31" s="17" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,722万
+$1722万
 $27,908/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,678万
+$1678万
 $27,191/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J31" s="17" t="inlineStr">
+      <c r="J30" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$1,997万
+$1997万
 $24,713/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 831呎 (2房)
-$2,089万
+$2089万
 $25,140/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 799呎 (3房)
-$1,989万
+$1989万
 $24,896/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 781呎 (3房)
-$1,944万
+$1944万
 $24,895/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 783呎 (3房)
-$1,949万
+$1949万
 $24,895/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 855呎 (3房)
-$2,150万
+$2150万
 $25,140/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 906呎 (3房)
-$2,267万
+$2267万
 $25,022/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 617呎 (2房)
-$1,718万
+$1718万
 $27,838/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 617呎 (2房)
-$1,674万
+$1674万
 $27,125/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J32" s="17" t="inlineStr">
+      <c r="J31" s="21" t="inlineStr">
         <is>
           <t>J | 808呎 (3房)
-$1,992万
+$1992万
 $24,651/呎
 (已售)</t>
         </is>
@@ -30855,7 +30893,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -30868,146 +30906,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>柏蔚山 - 2座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>187 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>184 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="18" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>B | 1006呎 (4+房)
 招标单位
@@ -31015,163 +31053,163 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>F | 1048呎 (4+房)
-$4,533万
+$4533万
 $43,254/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>G | 1077呎 (4+房)
-$4,835万
+$4835万
 $44,892/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2058呎 (4+房)
+$10496万
+$51,000/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1856呎 (4+房)
+$9317万
+$50,200/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 2028呎 (4+房)
+$10500万
+$51,774/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1014呎 (4+房)
-$4,398万
+$4398万
 $43,370/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1048呎 (4+房)
-$4,284万
+$4284万
 $40,874/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 1075呎 (4+房)
-$3,477万
+$3477万
 $32,347/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>33&amp;35/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 2058呎 (4+房)
-$10,496万
-$51,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 1856呎 (4+房)
-$9,317万
-$50,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 2028呎 (4+房)
-$10,500万
-$51,774/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr"/>
-      <c r="H8" s="16" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 1271呎 (4+房)
-$5,618万
+$5618万
 $44,197/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 994呎 (4+房)
-$4,226万
+$4226万
 $42,519/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 1066呎 (3房)
-$4,478万
+$4478万
 $42,008/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>E | 999呎 (4+房)
-$4,483万
+$4483万
 $44,875/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 1032呎 (4+房)
-$4,295万
+$4295万
 $41,614/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 1109呎 (4+房)
-$4,785万
+$4785万
 $43,149/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1271呎 (4+房)
 招标单位
@@ -31179,170 +31217,170 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 994呎 (4+房)
-$4,264万
+$4264万
 $42,897/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 1066呎 (3房)
-$4,348万
+$4348万
 $40,783/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>E | 999呎 (4+房)
-$2,960万
+$2960万
 $29,627/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 1032呎 (4+房)
-$4,170万
+$4170万
 $40,402/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 1109呎 (4+房)
-$4,646万
+$4646万
 $41,893/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1271呎 (4+房)
-$5,194万
+$5194万
 $40,869/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 994呎 (4+房)
-$3,840万
+$3840万
 $38,630/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 1066呎 (3房)
-$4,221万
+$4221万
 $39,596/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 999呎 (4+房)
-$4,226万
+$4226万
 $42,298/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 1033呎 (4+房)
-$4,048万
+$4048万
 $39,188/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 1109呎 (4+房)
-$4,511万
+$4511万
 $40,673/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 1271呎 (4+房)
-$4,836万
+$4836万
 $38,046/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 994呎 (4+房)
-$3,682万
+$3682万
 $37,038/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 1066呎 (3房)
-$3,998万
+$3998万
 $37,505/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 999呎 (4+房)
-$3,954万
+$3954万
 $39,583/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 1033呎 (4+房)
-$3,788万
+$3788万
 $36,672/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 1109呎 (4+房)
-$4,379万
+$4379万
 $39,488/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1271呎 (4+房)
 招标单位
@@ -31350,1365 +31388,1365 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 994呎 (4+房)
-$3,728万
+$3728万
 $37,505/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 1066呎 (3房)
-$4,098万
+$4098万
 $38,443/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 999呎 (4+房)
-$4,103万
+$4103万
 $41,067/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 1032呎 (4+房)
-$2,821万
+$2821万
 $27,333/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 1109呎 (4+房)
-$4,379万
+$4379万
 $39,488/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 1271呎 (4+房)
-$4,650万
+$4650万
 $36,583/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 994呎 (4+房)
-$3,655万
+$3655万
 $36,770/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 1066呎 (3房)
-$4,018万
+$4018万
 $37,689/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 999呎 (4+房)
-$4,022万
+$4022万
 $40,261/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 1032呎 (4+房)
-$2,765万
+$2765万
 $26,797/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 1109呎 (4+房)
-$4,293万
+$4293万
 $38,713/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 1271呎 (4+房)
-$4,559万
+$4559万
 $35,866/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 994呎 (4+房)
-$3,811万
+$3811万
 $38,339/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 1066呎 (3房)
-$4,087万
+$4087万
 $38,340/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 999呎 (4+房)
-$3,118万
+$3118万
 $31,211/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 1032呎 (4+房)
-$3,769万
+$3769万
 $36,522/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 1109呎 (4+房)
-$4,097万
+$4097万
 $36,945/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,730万
+$2730万
 $33,913/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,726万
+$2726万
 $33,128/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$2,095万
+$2095万
 $34,631/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,729万
+$2729万
 $33,774/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 677呎 (2房)
-$2,099万
+$2099万
 $31,006/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 837呎 (3房)
-$2,447万
+$2447万
 $29,233/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,726万
+$2726万
 $30,028/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,486万
+$2486万
 $29,994/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,650万
+$2650万
 $32,925/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,637万
+$2637万
 $32,046/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$2,027万
+$2027万
 $33,502/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,624万
+$2624万
 $32,475/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 678呎 (2房)
-$2,018万
+$2018万
 $29,770/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 837呎 (3房)
-$2,411万
+$2411万
 $28,802/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,686万
+$2686万
 $29,584/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,450万
+$2450万
 $29,551/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,573万
+$2573万
 $31,966/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,561万
+$2561万
 $31,113/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,968万
+$1968万
 $32,527/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,523万
+$2523万
 $31,225/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 678呎 (2房)
-$1,941万
+$1941万
 $28,624/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,375万
+$2375万
 $28,341/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,646万
+$2646万
 $29,146/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,414万
+$2414万
 $29,115/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,548万
+$2548万
 $31,650/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,544万
+$2544万
 $30,916/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,955万
+$1955万
 $32,321/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,498万
+$2498万
 $30,916/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 678呎 (2房)
-$1,922万
+$1922万
 $28,341/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,340万
+$2340万
 $27,924/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 909呎 (3房)
-$2,607万
+$2607万
 $28,684/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,378万
+$2378万
 $28,685/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 804呎 (3房)
-$2,523万
+$2523万
 $31,376/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,519万
+$2519万
 $30,610/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,917万
+$1917万
 $31,688/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,473万
+$2473万
 $30,610/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 678呎 (2房)
-$1,902万
+$1902万
 $28,059/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 837呎 (3房)
-$2,305万
+$2305万
 $27,542/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 909呎 (3房)
-$2,569万
+$2569万
 $28,260/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,343万
+$2343万
 $28,261/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 804呎 (3房)
-$2,498万
+$2498万
 $31,065/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,494万
+$2494万
 $30,307/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,880万
+$1880万
 $31,066/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,449万
+$2449万
 $30,307/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 678呎 (2房)
-$1,884万
+$1884万
 $27,782/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,724万
+$2724万
 $32,506/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,556万
+$2556万
 $28,151/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,331万
+$2331万
 $28,121/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 804呎 (3房)
-$2,498万
+$2498万
 $31,065/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,494万
+$2494万
 $30,307/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,880万
+$1880万
 $31,066/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,449万
+$2449万
 $30,307/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 677呎 (2房)
-$1,884万
+$1884万
 $27,823/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,294万
+$2294万
 $27,374/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,556万
+$2556万
 $28,151/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,331万
+$2331万
 $28,121/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,449万
+$2449万
 $30,419/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,445万
+$2445万
 $29,713/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,843万
+$1843万
 $30,456/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,851万
+$2851万
 $35,285/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 677呎 (2房)
-$1,847万
+$1847万
 $27,278/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,271万
+$2271万
 $27,103/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,531万
+$2531万
 $27,872/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,308万
+$2308万
 $27,841/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,424万
+$2424万
 $30,117/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,550万
+$2550万
 $30,982/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,824万
+$1824万
 $30,155/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,377万
+$2377万
 $29,420/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 678呎 (2房)
-$2,171万
+$2171万
 $32,025/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,380万
+$2380万
 $28,400/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 909呎 (3房)
-$2,518万
+$2518万
 $27,703/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,297万
+$2297万
 $27,703/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 804呎 (3房)
-$2,400万
+$2400万
 $29,856/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,397万
+$2397万
 $29,128/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,806万
+$1806万
 $29,856/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,354万
+$2354万
 $29,127/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 678呎 (2房)
-$1,819万
+$1819万
 $26,833/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,249万
+$2249万
 $26,833/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,506万
+$2506万
 $27,595/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,285万
+$2285万
 $27,566/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,377万
+$2377万
 $29,524/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,374万
+$2374万
 $28,840/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,788万
+$1788万
 $29,560/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,330万
+$2330万
 $28,839/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 677呎 (2房)
-$1,810万
+$1810万
 $26,740/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 837呎 (3房)
-$2,238万
+$2238万
 $26,732/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 909呎 (3房)
-$2,493万
+$2493万
 $27,428/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,274万
+$2274万
 $27,428/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 804呎 (3房)
-$2,330万
+$2330万
 $28,980/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,327万
+$2327万
 $28,273/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,753万
+$1753万
 $28,980/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,284万
+$2284万
 $28,274/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 677呎 (2房)
-$1,801万
+$1801万
 $26,606/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,226万
+$2226万
 $26,567/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 909呎 (3房)
-$2,481万
+$2481万
 $27,292/呎
 (18年-06月)</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,262万
+$2262万
 $27,291/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 804呎 (3房)
-$2,284万
+$2284万
 $28,413/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,402万
+$2402万
 $29,192/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,719万
+$1719万
 $28,413/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,240万
+$2240万
 $27,719/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 677呎 (2房)
-$1,792万
+$1792万
 $26,474/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,215万
+$2215万
 $26,434/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,468万
+$2468万
 $27,185/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,251万
+$2251万
 $27,156/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,273万
+$2273万
 $28,236/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,270万
+$2270万
 $27,582/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,710万
+$1710万
 $28,271/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,229万
+$2229万
 $27,582/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 678呎 (2房)
-$1,788万
+$1788万
 $26,369/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 838呎 (3房)
-$2,210万
+$2210万
 $26,369/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 909呎 (3房)
-$2,462万
+$2462万
 $27,088/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,246万
+$2246万
 $27,088/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,273万
+$2273万
 $28,236/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,270万
+$2270万
 $27,582/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,710万
+$1710万
 $28,271/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,229万
+$2229万
 $27,582/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 677呎 (2房)
-$1,788万
+$1788万
 $26,408/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 837呎 (3房)
-$2,210万
+$2210万
 $26,400/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 909呎 (3房)
-$2,462万
+$2462万
 $27,088/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,246万
+$2246万
 $27,088/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 804呎 (3房)
-$2,250万
+$2250万
 $27,991/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,248万
+$2248万
 $27,309/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,694万
+$1694万
 $27,992/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,206万
+$2206万
 $27,308/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 678呎 (2房)
-$1,779万
+$1779万
 $26,237/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 837呎 (3房)
-$2,199万
+$2199万
 $26,269/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H31" s="17" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,450万
+$2450万
 $26,982/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,234万
+$2234万
 $26,953/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,239万
+$2239万
 $27,817/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 823呎 (3房)
-$2,236万
+$2236万
 $27,173/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 605呎 (2房)
-$1,685万
+$1685万
 $27,853/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 808呎 (3房)
-$2,196万
+$2196万
 $27,173/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 677呎 (2房)
-$1,774万
+$1774万
 $26,211/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 837呎 (3房)
-$2,193万
+$2193万
 $26,203/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,444万
+$2444万
 $26,916/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 829呎 (3房)
-$2,229万
+$2229万
 $26,885/呎
 (已售)</t>
         </is>
@@ -32716,7 +32754,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -32729,2062 +32767,2062 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>柏蔚山 - 3座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>213 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>213 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 662呎 (1房)
-$3,106万
+$3106万
 $46,920/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>F | 908呎 (3房)
-$2,811万
+$2811万
 $30,956/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>G | 907呎 (3房)
-$2,897万
+$2897万
 $31,938/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>H | 834呎 (3房)
-$2,712万
+$2712万
 $32,518/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33&amp;35</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2503呎 (4+房)
+$12510万
+$49,980/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1624呎 (4+房)
+$8206万
+$50,531/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 2282呎 (4+房)
+$11684万
+$51,200/呎
+(已售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 662呎 (1房)
-$2,895万
+$2895万
 $43,731/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 908呎 (3房)
-$2,902万
+$2902万
 $31,961/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,840万
+$2840万
 $31,278/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 834呎 (3房)
-$2,659万
+$2659万
 $31,880/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>33&amp;35/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 2503呎 (4+房)
-$12,510万
-$49,980/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 1624呎 (4+房)
-$8,206万
-$50,531/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 2282呎 (4+房)
-$11,684万
-$51,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr"/>
-      <c r="H8" s="16" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
-      <c r="J8" s="16" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 1511呎 (4+房)
-$6,938万
+$6938万
 $45,919/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 616呎 (1房)
-$2,586万
+$2586万
 $41,982/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
-$3,169万
+$3169万
 $39,657/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 1230呎 (4+房)
-$5,007万
+$5007万
 $40,708/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 882呎 (3房)
-$2,621万
+$2621万
 $29,720/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$3,306万
+$3306万
 $36,414/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>H | 833呎 (3房)
-$2,529万
+$2529万
 $30,361/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 1536呎 (4+房)
-$6,689万
+$6689万
 $43,546/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 616呎 (1房)
-$2,403万
+$2403万
 $39,006/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 798呎 (3房)
-$3,018万
+$3018万
 $37,816/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 1230呎 (4+房)
-$4,769万
+$4769万
 $38,770/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 882呎 (3房)
-$2,570万
+$2570万
 $29,138/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,730万
+$2730万
 $30,064/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>H | 833呎 (3房)
-$2,480万
+$2480万
 $29,767/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1512呎 (4+房)
-$5,606万
+$5606万
 $37,077/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 616呎 (1房)
-$2,333万
+$2333万
 $37,870/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
-$2,794万
+$2794万
 $34,971/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 1230呎 (4+房)
-$4,630万
+$4630万
 $37,641/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 882呎 (3房)
-$2,520万
+$2520万
 $28,567/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,676万
+$2676万
 $29,475/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>H | 833呎 (3房)
-$2,431万
+$2431万
 $29,182/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 1536呎 (4+房)
-$5,496万
+$5496万
 $35,781/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 615呎 (1房)
-$2,287万
+$2287万
 $37,190/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 798呎 (3房)
-$2,739万
+$2739万
 $34,328/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 1230呎 (4+房)
-$4,539万
+$4539万
 $36,902/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 882呎 (3房)
-$2,470万
+$2470万
 $28,007/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,624万
+$2624万
 $28,896/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>H | 833呎 (3房)
-$2,383万
+$2383万
 $28,610/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 1512呎 (4+房)
-$6,024万
+$6024万
 $39,839/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 616呎 (1房)
-$2,287万
+$2287万
 $37,130/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 798呎 (3房)
-$3,005万
+$3005万
 $37,658/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 1230呎 (4+房)
-$4,539万
+$4539万
 $36,902/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 881呎 (3房)
-$2,470万
+$2470万
 $28,039/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 907呎 (3房)
-$2,624万
+$2624万
 $28,928/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>H | 833呎 (3房)
-$2,383万
+$2383万
 $28,610/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 1537呎 (4+房)
-$5,792万
+$5792万
 $37,684/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 616呎 (1房)
-$2,199万
+$2199万
 $35,701/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 799呎 (3房)
-$2,744万
+$2744万
 $34,340/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 1230呎 (4+房)
-$4,364万
+$4364万
 $35,483/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 881呎 (3房)
-$2,384万
+$2384万
 $27,065/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 907呎 (3房)
-$2,533万
+$2533万
 $27,923/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>H | 833呎 (3房)
-$2,300万
+$2300万
 $27,616/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 1511呎 (4+房)
-$5,820万
+$5820万
 $38,520/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 616呎 (1房)
-$2,156万
+$2156万
 $35,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 798呎 (3房)
-$2,690万
+$2690万
 $33,709/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 1230呎 (4+房)
-$4,279万
+$4279万
 $34,787/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 881呎 (3房)
-$2,338万
+$2338万
 $26,533/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 908呎 (3房)
-$2,483万
+$2483万
 $27,346/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 833呎 (3房)
-$2,255万
+$2255万
 $27,074/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,953万
+$1953万
 $29,768/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,790万
+$1790万
 $31,400/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,605万
+$1605万
 $30,919/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,664万
+$1664万
 $30,367/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,542万
+$2542万
 $28,979/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,300万
+$2300万
 $26,014/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 911呎 (3房)
-$2,442万
+$2442万
 $26,810/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,622万
+$2622万
 $31,520/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,523万
+$2523万
 $28,703/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (1房)
-$1,896万
+$1896万
 $28,947/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,650万
+$1650万
 $28,947/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,558万
+$1558万
 $30,019/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,616万
+$1616万
 $29,482/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,444万
+$2444万
 $27,864/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,266万
+$2266万
 $25,629/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 911呎 (3房)
-$2,406万
+$2406万
 $26,413/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,176万
+$2176万
 $26,151/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,426万
+$2426万
 $27,600/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,841万
+$1841万
 $28,061/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,602万
+$1602万
 $28,104/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,513万
+$1513万
 $29,145/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,608万
+$1608万
 $29,339/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,373万
+$2373万
 $27,054/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,232万
+$2232万
 $25,250/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,371万
+$2371万
 $25,995/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,144万
+$2144万
 $25,764/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,355万
+$2355万
 $26,795/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,822万
+$1822万
 $27,782/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,586万
+$1586万
 $27,825/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,535万
+$1535万
 $29,578/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,553万
+$1553万
 $28,341/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,338万
+$2338万
 $26,653/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,301万
+$2301万
 $26,031/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 911呎 (3房)
-$2,336万
+$2336万
 $25,638/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,112万
+$2112万
 $25,385/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,320万
+$2320万
 $26,399/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,804万
+$1804万
 $27,508/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,570万
+$1570万
 $27,551/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,520万
+$1520万
 $29,285/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,576万
+$1576万
 $28,763/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,303万
+$2303万
 $26,260/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,267万
+$2267万
 $25,646/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,301万
+$2301万
 $25,232/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,081万
+$2081万
 $25,010/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J20" s="17" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,286万
+$2286万
 $26,010/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (1房)
-$1,787万
+$1787万
 $27,278/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,590万
+$1590万
 $27,891/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,541万
+$1541万
 $29,686/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,596万
+$1596万
 $29,131/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,292万
+$2292万
 $26,129/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,256万
+$2256万
 $25,518/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,411万
+$2411万
 $26,440/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,395万
+$2395万
 $28,781/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J21" s="17" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,275万
+$2275万
 $25,879/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (1房)
-$1,787万
+$1787万
 $27,278/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,555万
+$1555万
 $27,277/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,468万
+$1468万
 $28,287/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,560万
+$1560万
 $28,476/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,292万
+$2292万
 $26,129/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,256万
+$2256万
 $25,518/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,411万
+$2411万
 $26,440/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,274万
+$2274万
 $27,329/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J22" s="17" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,701万
+$2701万
 $30,733/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,752万
+$1752万
 $26,701/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,524万
+$1524万
 $26,742/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,475万
+$1475万
 $28,426/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,530万
+$1530万
 $27,918/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,269万
+$2269万
 $25,870/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,234万
+$2234万
 $25,266/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,287万
+$2287万
 $25,077/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,089万
+$2089万
 $25,105/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,252万
+$2252万
 $25,625/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,734万
+$1734万
 $26,438/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,509万
+$1509万
 $26,477/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,425万
+$1425万
 $27,459/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,478万
+$1478万
 $26,969/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,258万
+$2258万
 $25,742/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,222万
+$2222万
 $25,140/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,440万
+$2440万
 $26,751/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,218万
+$2218万
 $26,660/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J24" s="17" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,661万
+$2661万
 $30,278/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (1房)
-$1,726万
+$1726万
 $26,345/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,577万
+$1577万
 $27,661/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,418万
+$1418万
 $27,322/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,543万
+$1543万
 $28,159/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,246万
+$2246万
 $25,613/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,211万
+$2211万
 $25,015/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,452万
+$2452万
 $26,885/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,229万
+$2229万
 $26,793/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J25" s="17" t="inlineStr">
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,230万
+$2230万
 $25,370/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (1房)
-$1,717万
+$1717万
 $26,215/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,774万
+$1774万
 $31,132/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,446万
+$1446万
 $27,865/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,500万
+$1500万
 $27,367/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,235万
+$2235万
 $25,487/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,200万
+$2200万
 $24,891/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,440万
+$2440万
 $26,750/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,218万
+$2218万
 $26,660/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J26" s="17" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,219万
+$2219万
 $25,243/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,708万
+$1708万
 $26,044/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,487万
+$1487万
 $26,084/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,404万
+$1404万
 $27,052/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,492万
+$1492万
 $27,232/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,224万
+$2224万
 $25,359/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,600万
+$2600万
 $29,411/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 911呎 (3房)
-$2,428万
+$2428万
 $26,648/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,202万
+$2202万
 $26,462/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J27" s="17" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,208万
+$2208万
 $25,118/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,700万
+$1700万
 $25,915/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,479万
+$1479万
 $25,954/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,397万
+$1397万
 $26,915/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,449万
+$1449万
 $26,436/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,213万
+$2213万
 $25,233/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,178万
+$2178万
 $24,644/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,416万
+$2416万
 $26,486/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,196万
+$2196万
 $26,395/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J28" s="17" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,324万
+$2324万
 $26,439/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,696万
+$1696万
 $25,851/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,513万
+$1513万
 $26,537/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,394万
+$1394万
 $26,850/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,481万
+$1481万
 $27,029/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,329万
+$2329万
 $26,561/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,173万
+$2173万
 $24,583/呎
 (18年-06月)</t>
         </is>
       </c>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,861万
+$2861万
 $31,373/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,191万
+$2191万
 $26,329/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J29" s="17" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,318万
+$2318万
 $26,374/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,696万
+$1696万
 $25,851/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,513万
+$1513万
 $26,537/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,394万
+$1394万
 $26,850/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,481万
+$1481万
 $27,029/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,329万
+$2329万
 $26,561/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,173万
+$2173万
 $24,583/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 912呎 (3房)
-$2,409万
+$2409万
 $26,419/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,191万
+$2191万
 $26,329/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J30" s="17" t="inlineStr">
+      <c r="J29" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,318万
+$2318万
 $26,374/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>A | 656呎 (1房)
-$1,687万
+$1687万
 $25,721/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,505万
+$1505万
 $26,405/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,421万
+$1421万
 $27,383/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,438万
+$1438万
 $26,239/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,318万
+$2318万
 $26,429/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,162万
+$2162万
 $24,460/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H31" s="17" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 911呎 (3房)
-$2,525万
+$2525万
 $27,715/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,180万
+$2180万
 $26,198/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J31" s="17" t="inlineStr">
+      <c r="J30" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,307万
+$2307万
 $26,243/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 655呎 (1房)
-$1,683万
+$1683万
 $25,698/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 570呎 (1房)
-$1,501万
+$1501万
 $26,340/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 519呎 (1房)
-$1,418万
+$1418万
 $27,314/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 548呎 (1房)
-$1,470万
+$1470万
 $26,827/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 877呎 (3房)
-$2,312万
+$2312万
 $26,363/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 884呎 (3房)
-$2,157万
+$2157万
 $24,398/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 911呎 (3房)
-$2,392万
+$2392万
 $26,251/呎
 (已售)</t>
         </is>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 832呎 (3房)
-$2,174万
+$2174万
 $26,133/呎
 (已售)</t>
         </is>
       </c>
-      <c r="J32" s="17" t="inlineStr">
+      <c r="J31" s="21" t="inlineStr">
         <is>
           <t>J | 879呎 (3房)
-$2,301万
+$2301万
 $26,177/呎
 (已售)</t>
         </is>
@@ -34792,7 +34830,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
